--- a/profit_summary.xlsx
+++ b/profit_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P4"/>
+  <dimension ref="A1:R24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,65 +446,75 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>DDC1</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>Total_profit1</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Profit1</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Acc_dividend1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>CAER1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>CAER_market1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>CAER_dividend1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Cost2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>DDC2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Total_profit2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Profit2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Acc_dividend2</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>CAER2</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>CAER_market2</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>CAER_dividend2</t>
         </is>
@@ -520,149 +530,1327 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1250</v>
+        <v>23557041</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>4254516779.200209</v>
       </c>
       <c r="E2" t="n">
-        <v>15</v>
+        <v>913505.1020820285</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>649870.1020820285</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0520889810917935</v>
+        <v>263635</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0520889810917935</v>
+        <v>0.05420847051740085</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>0.03191724801433882</v>
       </c>
       <c r="J2" t="n">
-        <v>1250</v>
+        <v>0.02253415714135487</v>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>17391.75</v>
       </c>
       <c r="L2" t="n">
-        <v>15</v>
+        <v>3107618.75810035</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>262.6624197997643</v>
       </c>
       <c r="N2" t="n">
-        <v>0.0520889810917935</v>
+        <v>71.94241979976424</v>
       </c>
       <c r="O2" t="n">
-        <v>0.0520889810917935</v>
+        <v>190.7199999999999</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>0.007029572527846195</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>-0.01469806367936599</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.02232455986730075</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMZN</t>
+          <t>Starbucks</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5</v>
+        <v>10.06451</v>
       </c>
       <c r="C3" t="n">
-        <v>250</v>
+        <v>984699</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>7640043</v>
       </c>
       <c r="E3" t="n">
-        <v>10</v>
+        <v>-27263</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-32534</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1001395866113319</v>
+        <v>5271</v>
       </c>
       <c r="H3" t="n">
-        <v>0.1001395866113319</v>
+        <v>-0.7361899736276639</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>-0.7965305867891421</v>
       </c>
       <c r="J3" t="n">
-        <v>250</v>
+        <v>0.2855004189299259</v>
       </c>
       <c r="K3" t="n">
-        <v>10</v>
+        <v>771.0200000000001</v>
       </c>
       <c r="L3" t="n">
-        <v>10</v>
+        <v>5908.64</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>-21.98000000000005</v>
       </c>
       <c r="N3" t="n">
-        <v>0.1001395866113319</v>
+        <v>-26.17000000000005</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1001395866113319</v>
+        <v>4.19</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>-0.7499937127587428</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.808610502127981</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2945094813973614</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TSLA</t>
+          <t>Coca-Cola</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>1000</v>
+        <v>3352360</v>
       </c>
       <c r="D4" t="n">
+        <v>599544261.5428572</v>
+      </c>
+      <c r="E4" t="n">
+        <v>106578</v>
+      </c>
+      <c r="F4" t="n">
+        <v>56673</v>
+      </c>
+      <c r="G4" t="n">
+        <v>49905.00000000001</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0.05185745334418135</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.0230252172626868</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0.03047664424396901</v>
+      </c>
+      <c r="K4" t="n">
+        <v>2523.11</v>
+      </c>
+      <c r="L4" t="n">
+        <v>429606.52</v>
+      </c>
+      <c r="M4" t="n">
+        <v>17.83000000000007</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-18.17999999999996</v>
+      </c>
+      <c r="O4" t="n">
+        <v>36.01</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0.003222501260567778</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>-0.02539498096738235</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.03070215224344031</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>SGOL</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>105</v>
+      </c>
+      <c r="C5" t="n">
+        <v>2375494</v>
+      </c>
+      <c r="D5" t="n">
+        <v>63357161</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-95602</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-95602</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-0.4300248994866178</v>
+      </c>
+      <c r="I5" t="n">
+        <v>-0.4300248994866178</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1853.16</v>
+      </c>
+      <c r="L5" t="n">
+        <v>49404.36</v>
+      </c>
+      <c r="M5" t="n">
+        <v>-102.99</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-102.99</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-0.5444772321087208</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.5444772321087208</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C6" t="n">
+        <v>1705896</v>
+      </c>
+      <c r="D6" t="n">
+        <v>603887184</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-211904</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-242857</v>
+      </c>
+      <c r="G6" t="n">
+        <v>30953</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-0.1278207350724535</v>
+      </c>
+      <c r="I6" t="n">
+        <v>-0.1464462835600957</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.01871377927645002</v>
+      </c>
+      <c r="K6" t="n">
+        <v>1305</v>
+      </c>
+      <c r="L6" t="n">
+        <v>461970</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-140.18</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-163.52</v>
+      </c>
+      <c r="O6" t="n">
+        <v>23.34</v>
+      </c>
+      <c r="P6" t="n">
+        <v>-0.1105638434156285</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.1289338921062307</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0.01844590274557811</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Alphabet</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>5.067042</v>
+      </c>
+      <c r="C7" t="n">
+        <v>1175281</v>
+      </c>
+      <c r="D7" t="n">
+        <v>101340891</v>
+      </c>
+      <c r="E7" t="n">
+        <v>21704.1020820285</v>
+      </c>
+      <c r="F7" t="n">
+        <v>21171.1020820285</v>
+      </c>
+      <c r="G7" t="n">
+        <v>533</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.01220720990140922</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.0104771666504031</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.001920765664910062</v>
+      </c>
+      <c r="K7" t="n">
+        <v>850.75</v>
+      </c>
+      <c r="L7" t="n">
+        <v>73095.19</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-17.33758020023581</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-17.70758020023582</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="P7" t="n">
+        <v>-0.1615888326738586</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>-0.1629760810019565</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.001848540997660075</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Dole</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>149</v>
+      </c>
+      <c r="C8" t="n">
+        <v>2640190</v>
+      </c>
+      <c r="D8" t="n">
+        <v>722201229.9324597</v>
+      </c>
+      <c r="E8" t="n">
+        <v>139701</v>
+      </c>
+      <c r="F8" t="n">
+        <v>106105</v>
+      </c>
+      <c r="G8" t="n">
+        <v>33596.00000000001</v>
+      </c>
+      <c r="H8" t="n">
+        <v>0.06237915574835129</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0.04615019901120632</v>
+      </c>
+      <c r="J8" t="n">
+        <v>0.01694901439723928</v>
+      </c>
+      <c r="K8" t="n">
+        <v>1951.21</v>
+      </c>
+      <c r="L8" t="n">
+        <v>524875.0237500001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>44.94</v>
+      </c>
+      <c r="N8" t="n">
+        <v>20.82</v>
+      </c>
+      <c r="O8" t="n">
+        <v>24.12</v>
+      </c>
+      <c r="P8" t="n">
+        <v>0.02323029265994503</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>0.007169591889137905</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.01674458903686227</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3.040697</v>
+      </c>
+      <c r="C9" t="n">
+        <v>896199</v>
+      </c>
+      <c r="D9" t="n">
+        <v>121570708</v>
+      </c>
+      <c r="E9" t="n">
+        <v>166922</v>
+      </c>
+      <c r="F9" t="n">
+        <v>165414</v>
+      </c>
+      <c r="G9" t="n">
+        <v>1508</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.5742997165307666</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.5685057065607424</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.004487740185291189</v>
+      </c>
+      <c r="K9" t="n">
+        <v>645.1299999999999</v>
+      </c>
+      <c r="L9" t="n">
+        <v>87552.57000000001</v>
+      </c>
+      <c r="M9" t="n">
+        <v>108.35</v>
+      </c>
+      <c r="N9" t="n">
+        <v>107.26</v>
+      </c>
+      <c r="O9" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="P9" t="n">
+        <v>0.5032997836228896</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.4976063705790739</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.004506014458460994</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Fresh Del Monte</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>47</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1752262</v>
+      </c>
+      <c r="D10" t="n">
+        <v>585873642.7083334</v>
+      </c>
+      <c r="E10" t="n">
+        <v>300956.9999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>237512</v>
+      </c>
+      <c r="G10" t="n">
+        <v>63445.00000000001</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.1605101481656859</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.1247645663575625</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.03926055359378955</v>
+      </c>
+      <c r="K10" t="n">
+        <v>1307.45</v>
+      </c>
+      <c r="L10" t="n">
+        <v>431808.97</v>
+      </c>
+      <c r="M10" t="n">
+        <v>162.04</v>
+      </c>
+      <c r="N10" t="n">
+        <v>116.19</v>
+      </c>
+      <c r="O10" t="n">
+        <v>45.85000000000001</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0.1148093082190984</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.07947179568791407</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0.03851947909727294</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2.016456</v>
+      </c>
+      <c r="C11" t="n">
+        <v>997528</v>
+      </c>
+      <c r="D11" t="n">
+        <v>243477313.983225</v>
+      </c>
+      <c r="E11" t="n">
+        <v>184566</v>
+      </c>
+      <c r="F11" t="n">
+        <v>179644</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4922</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.2813566180267275</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.2736225449228407</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.00738417534202096</v>
+      </c>
+      <c r="K11" t="n">
+        <v>754.0700000000001</v>
+      </c>
+      <c r="L11" t="n">
+        <v>185979.74435035</v>
+      </c>
+      <c r="M11" t="n">
+        <v>88.20999999999999</v>
+      </c>
+      <c r="N11" t="n">
+        <v>84.55999999999999</v>
+      </c>
+      <c r="O11" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0.1713002371316379</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0.1640040195458889</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.007168623623187598</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Meta</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.012306</v>
+      </c>
+      <c r="C12" t="n">
+        <v>10974</v>
+      </c>
+      <c r="D12" t="n">
+        <v>1380456</v>
+      </c>
+      <c r="E12" t="n">
+        <v>-1148</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-1162</v>
+      </c>
+      <c r="G12" t="n">
+        <v>14</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-0.4346441568426772</v>
+      </c>
+      <c r="I12" t="n">
+        <v>-0.4374829829734227</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.003705935137639838</v>
+      </c>
+      <c r="K12" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1002.96</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.8200000000000001</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-0.83</v>
+      </c>
+      <c r="O12" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-0.401280356258554</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>-0.4041982336347205</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.003643206058132398</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Archer-Daniels-Midland</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
         <v>5</v>
       </c>
-      <c r="E4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.02634758527775505</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.02634758527775505</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0.02634758527775505</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0.02634758527775505</v>
-      </c>
-      <c r="P4" t="n">
+      <c r="C13" t="n">
+        <v>542181</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3795267</v>
+      </c>
+      <c r="E13" t="n">
+        <v>-16489</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-16489</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.8001925392322818</v>
+      </c>
+      <c r="I13" t="n">
+        <v>-0.8001925392322818</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" t="n">
+        <v>410.99</v>
+      </c>
+      <c r="L13" t="n">
+        <v>2876.93</v>
+      </c>
+      <c r="M13" t="n">
+        <v>-16.74000000000001</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-16.74000000000001</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-0.8856270535690414</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.8856270535690414</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Civitas</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>20</v>
+      </c>
+      <c r="C14" t="n">
+        <v>423990</v>
+      </c>
+      <c r="D14" t="n">
+        <v>95249353.5</v>
+      </c>
+      <c r="E14" t="n">
+        <v>-34251</v>
+      </c>
+      <c r="F14" t="n">
+        <v>-34251</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-0.2480355578443578</v>
+      </c>
+      <c r="I14" t="n">
+        <v>-0.2480355578443578</v>
+      </c>
+      <c r="J14" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" t="n">
+        <v>321.4</v>
+      </c>
+      <c r="L14" t="n">
+        <v>72202.50999999999</v>
+      </c>
+      <c r="M14" t="n">
+        <v>-30.24999999999998</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-30.24999999999998</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" t="n">
+        <v>-0.2655963185787559</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.2655963185787559</v>
+      </c>
+      <c r="R14" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>6</v>
+      </c>
+      <c r="C15" t="n">
+        <v>1415419</v>
+      </c>
+      <c r="D15" t="n">
+        <v>539060354.5</v>
+      </c>
+      <c r="E15" t="n">
+        <v>-44330</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-85953</v>
+      </c>
+      <c r="G15" t="n">
+        <v>41623</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-0.03248794322584458</v>
+      </c>
+      <c r="I15" t="n">
+        <v>-0.06088935678370166</v>
+      </c>
+      <c r="J15" t="n">
+        <v>0.02810565649805419</v>
+      </c>
+      <c r="K15" t="n">
+        <v>1015.65</v>
+      </c>
+      <c r="L15" t="n">
+        <v>385799.08</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-65.25999999999999</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-94.78</v>
+      </c>
+      <c r="O15" t="n">
+        <v>29.52</v>
+      </c>
+      <c r="P15" t="n">
+        <v>-0.06480729321949141</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>-0.09320140060942217</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0.02785485362121909</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Pfizer</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>12</v>
+      </c>
+      <c r="C16" t="n">
+        <v>426773</v>
+      </c>
+      <c r="D16" t="n">
+        <v>68502075</v>
+      </c>
+      <c r="E16" t="n">
+        <v>-5138</v>
+      </c>
+      <c r="F16" t="n">
+        <v>-14739</v>
+      </c>
+      <c r="G16" t="n">
+        <v>9601</v>
+      </c>
+      <c r="H16" t="n">
+        <v>-0.03028989082091127</v>
+      </c>
+      <c r="I16" t="n">
+        <v>-0.08060052805416362</v>
+      </c>
+      <c r="J16" t="n">
+        <v>0.05185544292872568</v>
+      </c>
+      <c r="K16" t="n">
+        <v>301.56</v>
+      </c>
+      <c r="L16" t="n">
+        <v>47992.98</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1.349999999999998</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-5.600000000000001</v>
+      </c>
+      <c r="O16" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0.008960971059489342</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.04393169076293768</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0.05360083163701956</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>SCHD</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>7</v>
+      </c>
+      <c r="C17" t="n">
+        <v>277222</v>
+      </c>
+      <c r="D17" t="n">
+        <v>109620458.8333333</v>
+      </c>
+      <c r="E17" t="n">
+        <v>46488.00000000001</v>
+      </c>
+      <c r="F17" t="n">
+        <v>37901.00000000001</v>
+      </c>
+      <c r="G17" t="n">
+        <v>8587</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0.1529415146568718</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0.1245741292178015</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0.02855647930633376</v>
+      </c>
+      <c r="K17" t="n">
+        <v>192.88</v>
+      </c>
+      <c r="L17" t="n">
+        <v>76271.09</v>
+      </c>
+      <c r="M17" t="n">
+        <v>24.79000000000002</v>
+      </c>
+      <c r="N17" t="n">
+        <v>18.76000000000002</v>
+      </c>
+      <c r="O17" t="n">
+        <v>6.030000000000001</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0.1176088453780832</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.08892497043294845</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0.02882104660159457</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Tesla</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>1.016743</v>
+      </c>
+      <c r="C18" t="n">
+        <v>366363</v>
+      </c>
+      <c r="D18" t="n">
+        <v>6541468</v>
+      </c>
+      <c r="E18" t="n">
+        <v>90663</v>
+      </c>
+      <c r="F18" t="n">
+        <v>90663</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>80.45954248624558</v>
+      </c>
+      <c r="I18" t="n">
+        <v>80.45954248624558</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>255.29</v>
+      </c>
+      <c r="L18" t="n">
+        <v>4552.48</v>
+      </c>
+      <c r="M18" t="n">
+        <v>67.92999999999998</v>
+      </c>
+      <c r="N18" t="n">
+        <v>67.92999999999998</v>
+      </c>
+      <c r="O18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" t="n">
+        <v>110.0138131345513</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>110.0138131345513</v>
+      </c>
+      <c r="R18" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>NVIDIA</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>5.055925</v>
+      </c>
+      <c r="C19" t="n">
+        <v>1089156</v>
+      </c>
+      <c r="D19" t="n">
+        <v>97535528</v>
+      </c>
+      <c r="E19" t="n">
+        <v>195017</v>
+      </c>
+      <c r="F19" t="n">
+        <v>194933</v>
+      </c>
+      <c r="G19" t="n">
+        <v>84.00000000000001</v>
+      </c>
+      <c r="H19" t="n">
+        <v>0.7354928970566454</v>
+      </c>
+      <c r="I19" t="n">
+        <v>0.7350916589092999</v>
+      </c>
+      <c r="J19" t="n">
+        <v>0.0003143749941205698</v>
+      </c>
+      <c r="K19" t="n">
+        <v>745.09</v>
+      </c>
+      <c r="L19" t="n">
+        <v>67016.64</v>
+      </c>
+      <c r="M19" t="n">
+        <v>147.31</v>
+      </c>
+      <c r="N19" t="n">
+        <v>147.25</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0.8051109459850998</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0.8046876517693782</v>
+      </c>
+      <c r="R19" t="n">
+        <v>0.0003268144362891245</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Tesla Bear</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>11</v>
+      </c>
+      <c r="C20" t="n">
+        <v>163222</v>
+      </c>
+      <c r="D20" t="n">
+        <v>3298302</v>
+      </c>
+      <c r="E20" t="n">
+        <v>3598</v>
+      </c>
+      <c r="F20" t="n">
+        <v>3039</v>
+      </c>
+      <c r="G20" t="n">
+        <v>559</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.3097016765292617</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0.2246125030107677</v>
+      </c>
+      <c r="J20" t="n">
+        <v>0.06362812165583231</v>
+      </c>
+      <c r="K20" t="n">
+        <v>112.18</v>
+      </c>
+      <c r="L20" t="n">
+        <v>2266.78</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.589999999999994</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.209999999999994</v>
+      </c>
+      <c r="O20" t="n">
+        <v>0.3800000000000001</v>
+      </c>
+      <c r="P20" t="n">
+        <v>0.3110974455248219</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>0.226292127119113</v>
+      </c>
+      <c r="R20" t="n">
+        <v>0.06291696469214503</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Palantir Bear</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3</v>
+      </c>
+      <c r="C21" t="n">
+        <v>62768</v>
+      </c>
+      <c r="D21" t="n">
+        <v>1192592</v>
+      </c>
+      <c r="E21" t="n">
+        <v>10608</v>
+      </c>
+      <c r="F21" t="n">
+        <v>10608</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>19.08057300617445</v>
+      </c>
+      <c r="I21" t="n">
+        <v>19.08057300617445</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>43.18</v>
+      </c>
+      <c r="L21" t="n">
+        <v>820.42</v>
+      </c>
+      <c r="M21" t="n">
+        <v>7.789999999999999</v>
+      </c>
+      <c r="N21" t="n">
+        <v>7.789999999999999</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>23.19761412720413</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>23.19761412720413</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P&amp;G</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>3</v>
+      </c>
+      <c r="C22" t="n">
+        <v>655480</v>
+      </c>
+      <c r="D22" t="n">
+        <v>104006490</v>
+      </c>
+      <c r="E22" t="n">
+        <v>-3064</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-9447</v>
+      </c>
+      <c r="G22" t="n">
+        <v>6383</v>
+      </c>
+      <c r="H22" t="n">
+        <v>-0.01072036853772007</v>
+      </c>
+      <c r="I22" t="n">
+        <v>-0.03284869853705352</v>
+      </c>
+      <c r="J22" t="n">
+        <v>0.02253414163615064</v>
+      </c>
+      <c r="K22" t="n">
+        <v>464.9</v>
+      </c>
+      <c r="L22" t="n">
+        <v>74207</v>
+      </c>
+      <c r="M22" t="n">
+        <v>-25.47999999999995</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-29.95999999999995</v>
+      </c>
+      <c r="O22" t="n">
+        <v>4.48</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-0.1214233456463095</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>-0.14190192901807</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.02216547377606815</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>General Mills</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>11</v>
+      </c>
+      <c r="C23" t="n">
+        <v>775324</v>
+      </c>
+      <c r="D23" t="n">
+        <v>78637744.2</v>
+      </c>
+      <c r="E23" t="n">
+        <v>-36941.99999999999</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-43592.99999999999</v>
+      </c>
+      <c r="G23" t="n">
+        <v>6651</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-0.1774934718733137</v>
+      </c>
+      <c r="I23" t="n">
+        <v>-0.2047976149000974</v>
+      </c>
+      <c r="J23" t="n">
+        <v>0.0311887837398086</v>
+      </c>
+      <c r="K23" t="n">
+        <v>539.38</v>
+      </c>
+      <c r="L23" t="n">
+        <v>55038.52</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-39.89000000000001</v>
+      </c>
+      <c r="N23" t="n">
+        <v>-44.56000000000002</v>
+      </c>
+      <c r="O23" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="P23" t="n">
+        <v>-0.2538637587938051</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-0.2794143572501058</v>
+      </c>
+      <c r="R23" t="n">
+        <v>0.03128902110362919</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>iShares Gold ETF</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>13</v>
+      </c>
+      <c r="C24" t="n">
+        <v>1468260</v>
+      </c>
+      <c r="D24" t="n">
+        <v>96804255</v>
+      </c>
+      <c r="E24" t="n">
+        <v>122834</v>
+      </c>
+      <c r="F24" t="n">
+        <v>122834</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.5563630679403859</v>
+      </c>
+      <c r="I24" t="n">
+        <v>0.5563630679403859</v>
+      </c>
+      <c r="J24" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" t="n">
+        <v>1020.7</v>
+      </c>
+      <c r="L24" t="n">
+        <v>67370.34999999999</v>
+      </c>
+      <c r="M24" t="n">
+        <v>50.46000000000004</v>
+      </c>
+      <c r="N24" t="n">
+        <v>50.46000000000004</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0.3025820656115557</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0.3025820656115554</v>
+      </c>
+      <c r="R24" t="n">
         <v>0</v>
       </c>
     </row>
